--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.15706659305398</v>
+        <v>2.950523321371272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.79274803076972</v>
+        <v>3.21632155500008</v>
       </c>
       <c r="E2" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F2" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.01998620018392</v>
+        <v>5.040747757529887</v>
       </c>
       <c r="D3" t="n">
-        <v>31.46380874759297</v>
+        <v>5.112868921483857</v>
       </c>
       <c r="E3" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F3" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.26483261015515</v>
+        <v>5.893035299150212</v>
       </c>
       <c r="D4" t="n">
-        <v>25.66861731671553</v>
+        <v>4.171150313966274</v>
       </c>
       <c r="E4" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F4" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.24095566221877</v>
+        <v>5.40165529511055</v>
       </c>
       <c r="D5" t="n">
-        <v>9.013878188659973</v>
+        <v>1.464755205657246</v>
       </c>
       <c r="E5" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F5" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.36173100064864</v>
+        <v>5.096281287605405</v>
       </c>
       <c r="D6" t="n">
-        <v>31.84958404340891</v>
+        <v>5.175557407053947</v>
       </c>
       <c r="E6" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F6" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>49.73890087018787</v>
+        <v>8.08257139140553</v>
       </c>
       <c r="D7" t="n">
-        <v>12.68017950172016</v>
+        <v>2.060529169029526</v>
       </c>
       <c r="E7" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F7" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.56577385952051</v>
+        <v>4.804438252172083</v>
       </c>
       <c r="D8" t="n">
-        <v>29.53277346355749</v>
+        <v>4.799075687828092</v>
       </c>
       <c r="E8" t="n">
-        <v>8.69506979746712</v>
+        <v>1.412948842088407</v>
       </c>
       <c r="F8" t="n">
-        <v>8.552394852393853</v>
+        <v>1.389764163514001</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
